--- a/data/trans_dic/P15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,15</t>
+          <t>4,44; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 16,6</t>
+          <t>8,87; 16,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,98</t>
+          <t>4,1; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 14,33</t>
+          <t>5,9; 14,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,45</t>
+          <t>3,32; 9,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,94</t>
+          <t>6,11; 13,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,77</t>
+          <t>7,34; 15,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,77</t>
+          <t>7,78; 12,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,71</t>
+          <t>4,34; 8,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 14,27</t>
+          <t>8,44; 13,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,33</t>
+          <t>6,26; 10,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 12,37</t>
+          <t>7,55; 12,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,73</t>
+          <t>2,39; 6,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,98</t>
+          <t>4,52; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,78</t>
+          <t>2,3; 6,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,36</t>
+          <t>2,87; 7,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,52</t>
+          <t>2,23; 5,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,15</t>
+          <t>4,0; 8,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,81</t>
+          <t>1,79; 4,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,68</t>
+          <t>4,91; 8,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,43</t>
+          <t>2,67; 5,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,9</t>
+          <t>4,58; 7,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,82</t>
+          <t>2,45; 4,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,27</t>
+          <t>4,33; 7,28</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,77</t>
+          <t>6,99; 13,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 20,51</t>
+          <t>12,54; 20,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,89</t>
+          <t>4,85; 10,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,73</t>
+          <t>4,65; 10,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,74</t>
+          <t>2,58; 7,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 16,22</t>
+          <t>8,61; 15,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,53</t>
+          <t>2,26; 6,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,38</t>
+          <t>5,6; 10,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,49</t>
+          <t>5,28; 9,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,84</t>
+          <t>11,7; 17,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,71</t>
+          <t>3,97; 7,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,09</t>
+          <t>5,7; 9,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 14,51</t>
+          <t>8,24; 14,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 12,36</t>
+          <t>6,07; 12,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 14,07</t>
+          <t>7,08; 13,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,55</t>
+          <t>4,13; 12,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,3</t>
+          <t>3,52; 8,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,9</t>
+          <t>2,84; 6,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,9</t>
+          <t>6,67; 12,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,63</t>
+          <t>2,06; 6,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,54</t>
+          <t>6,68; 11,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,57</t>
+          <t>4,87; 8,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,41</t>
+          <t>7,83; 12,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,89</t>
+          <t>3,17; 7,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 14,41</t>
+          <t>5,72; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,19</t>
+          <t>3,45; 10,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,02</t>
+          <t>2,6; 8,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,3</t>
+          <t>1,91; 7,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,39</t>
+          <t>3,38; 10,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,58</t>
+          <t>5,5; 13,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,74</t>
+          <t>0,54; 5,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,9</t>
+          <t>5,62; 11,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,65</t>
+          <t>5,4; 10,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,57</t>
+          <t>1,94; 5,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,77</t>
+          <t>0,95; 3,9</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,88</t>
+          <t>4,46; 10,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,68</t>
+          <t>7,59; 15,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,17</t>
+          <t>7,33; 14,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 13,41</t>
+          <t>6,94; 13,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,51</t>
+          <t>4,81; 11,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 17,06</t>
+          <t>8,8; 17,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 18,16</t>
+          <t>9,72; 17,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,0; 13,52</t>
+          <t>7,96; 13,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,19</t>
+          <t>5,55; 10,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,99</t>
+          <t>9,27; 14,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,54; 15,24</t>
+          <t>9,44; 15,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,73</t>
+          <t>8,22; 12,34</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,95</t>
+          <t>5,5; 9,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,46</t>
+          <t>7,82; 12,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,96</t>
+          <t>2,65; 5,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,48</t>
+          <t>4,96; 9,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,68</t>
+          <t>2,42; 5,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,94</t>
+          <t>6,57; 10,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,67</t>
+          <t>2,56; 5,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,5</t>
+          <t>2,53; 8,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,92</t>
+          <t>4,35; 7,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,05</t>
+          <t>7,85; 10,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,24</t>
+          <t>2,97; 5,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,05</t>
+          <t>3,82; 8,1</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,85</t>
+          <t>4,88; 8,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,65</t>
+          <t>2,01; 4,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,06</t>
+          <t>3,15; 6,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,42</t>
+          <t>1,12; 4,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,12</t>
+          <t>4,55; 7,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,71</t>
+          <t>2,15; 4,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,76</t>
+          <t>2,14; 4,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,41</t>
+          <t>2,95; 5,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,57</t>
+          <t>5,22; 7,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,12</t>
+          <t>2,33; 4,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,94</t>
+          <t>2,94; 4,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,44</t>
+          <t>2,0; 4,41</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,33</t>
+          <t>6,48; 8,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,43</t>
+          <t>7,45; 9,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,7</t>
+          <t>5,14; 6,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,87</t>
+          <t>4,44; 6,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,11</t>
+          <t>4,5; 6,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,16</t>
+          <t>6,47; 8,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,2</t>
+          <t>4,62; 6,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,79</t>
+          <t>4,72; 6,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,93</t>
+          <t>5,74; 7,01</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,48</t>
+          <t>7,08; 8,47</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,22</t>
+          <t>5,12; 6,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,49</t>
+          <t>4,95; 6,47</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12019; 27717</t>
+          <t>12122; 28520</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25706; 48917</t>
+          <t>26142; 49492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11689; 29326</t>
+          <t>12038; 30533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18039; 44618</t>
+          <t>18361; 44750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8336; 24646</t>
+          <t>8660; 24434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18470; 40046</t>
+          <t>17545; 39323</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21097; 42654</t>
+          <t>21190; 45026</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22189; 36983</t>
+          <t>22542; 37127</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23676; 46501</t>
+          <t>23156; 46358</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50430; 83036</t>
+          <t>49116; 81308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37280; 65996</t>
+          <t>36488; 63547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45678; 74381</t>
+          <t>45387; 75641</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12553; 33170</t>
+          <t>11808; 30889</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22545; 45373</t>
+          <t>22862; 45243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11260; 29066</t>
+          <t>11580; 30468</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14655; 38177</t>
+          <t>14888; 38313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11008; 27814</t>
+          <t>11224; 29572</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20837; 42667</t>
+          <t>20951; 42477</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9122; 25182</t>
+          <t>9379; 25795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24669; 44704</t>
+          <t>25273; 44809</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27825; 54172</t>
+          <t>26581; 51893</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48077; 81272</t>
+          <t>47157; 78566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23975; 49436</t>
+          <t>25137; 48707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44004; 75172</t>
+          <t>44744; 75178</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22011; 43919</t>
+          <t>22272; 43138</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41356; 66452</t>
+          <t>40644; 67457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15562; 34703</t>
+          <t>15445; 33915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14203; 30764</t>
+          <t>14693; 32277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9055; 25955</t>
+          <t>8656; 25058</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30044; 55310</t>
+          <t>29356; 53691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7335; 21949</t>
+          <t>7589; 22368</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19707; 36225</t>
+          <t>19560; 36160</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35278; 62083</t>
+          <t>34569; 61004</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77572; 112011</t>
+          <t>77816; 113934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26397; 50471</t>
+          <t>26021; 49355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37869; 60443</t>
+          <t>37916; 61616</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28581; 52032</t>
+          <t>29565; 52924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21951; 46210</t>
+          <t>22684; 46231</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26638; 52060</t>
+          <t>26204; 51463</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13869; 39220</t>
+          <t>12923; 37813</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13250; 30814</t>
+          <t>13088; 31288</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10725; 26822</t>
+          <t>11062; 26997</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25139; 49946</t>
+          <t>25838; 49289</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9207; 31542</t>
+          <t>9790; 32658</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46079; 76929</t>
+          <t>48751; 80694</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35176; 65374</t>
+          <t>37191; 66995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59688; 93974</t>
+          <t>59318; 94683</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26734; 62230</t>
+          <t>24992; 62967</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12349; 29294</t>
+          <t>11632; 30677</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7081; 21662</t>
+          <t>7341; 22134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5491; 16930</t>
+          <t>5497; 17722</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3391; 14839</t>
+          <t>3408; 14032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6944; 21574</t>
+          <t>7023; 21376</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12231; 29820</t>
+          <t>12070; 30591</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1118; 10366</t>
+          <t>1181; 11289</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2969</t>
+          <t>0; 3262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22582; 44813</t>
+          <t>23100; 46036</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24674; 46047</t>
+          <t>23340; 44868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8658; 23941</t>
+          <t>8324; 23297</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3780; 14609</t>
+          <t>3673; 15118</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11702; 29460</t>
+          <t>12092; 29633</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21540; 42948</t>
+          <t>20797; 42858</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19630; 39925</t>
+          <t>19277; 38380</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18755; 36162</t>
+          <t>18708; 36212</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13419; 32011</t>
+          <t>13388; 31190</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26767; 47781</t>
+          <t>24636; 47689</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26121; 49609</t>
+          <t>26536; 48258</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20556; 34762</t>
+          <t>20450; 35123</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31094; 55957</t>
+          <t>30478; 56211</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51901; 83055</t>
+          <t>51342; 82003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51142; 81735</t>
+          <t>50619; 81994</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43352; 67049</t>
+          <t>43280; 64972</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33345; 61186</t>
+          <t>33839; 61208</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51871; 82609</t>
+          <t>51855; 82788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17787; 39137</t>
+          <t>17414; 38555</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31085; 59177</t>
+          <t>30970; 59570</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15792; 36233</t>
+          <t>15436; 33896</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46890; 75912</t>
+          <t>45585; 75268</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17903; 39211</t>
+          <t>17679; 40566</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25607; 72190</t>
+          <t>21447; 73560</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54167; 86684</t>
+          <t>54541; 88107</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106416; 149941</t>
+          <t>106490; 147921</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41044; 70661</t>
+          <t>39980; 70046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56076; 118634</t>
+          <t>56359; 119374</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36840; 65832</t>
+          <t>36311; 63259</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14882; 36256</t>
+          <t>15629; 36628</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24377; 47205</t>
+          <t>24536; 48204</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9780; 41033</t>
+          <t>10361; 41222</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36405; 63651</t>
+          <t>35674; 62623</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17141; 38780</t>
+          <t>17729; 38573</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17608; 39328</t>
+          <t>17717; 38422</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20986; 38853</t>
+          <t>21205; 39507</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>77936; 115686</t>
+          <t>79669; 117879</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36577; 66079</t>
+          <t>37326; 69570</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47824; 79336</t>
+          <t>47180; 79161</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>31824; 73064</t>
+          <t>32849; 72603</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>213412; 272920</t>
+          <t>212290; 275280</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>254257; 323070</t>
+          <t>255444; 320308</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>172348; 227456</t>
+          <t>174325; 228532</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>156189; 237795</t>
+          <t>153650; 236555</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>151081; 206321</t>
+          <t>151993; 204526</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>226504; 290278</t>
+          <t>230061; 294681</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>166967; 219653</t>
+          <t>163810; 219660</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>177727; 248580</t>
+          <t>172841; 242043</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>379017; 461354</t>
+          <t>381713; 466311</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>498305; 592513</t>
+          <t>494687; 591726</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>354579; 431587</t>
+          <t>355480; 430098</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>354667; 462516</t>
+          <t>352614; 461129</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,45</t>
+          <t>4,34; 10,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,79</t>
+          <t>9,21; 17,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,39</t>
+          <t>4,31; 9,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 14,37</t>
+          <t>5,72; 12,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,37</t>
+          <t>3,0; 9,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,69</t>
+          <t>6,34; 13,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,6</t>
+          <t>6,74; 14,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,82</t>
+          <t>7,38; 12,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,68</t>
+          <t>4,46; 8,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,97</t>
+          <t>8,62; 14,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,91</t>
+          <t>6,47; 11,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 12,58</t>
+          <t>7,29; 11,46</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,26</t>
+          <t>2,54; 6,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,95</t>
+          <t>4,54; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,06</t>
+          <t>2,43; 5,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,39</t>
+          <t>2,86; 7,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,87</t>
+          <t>2,21; 5,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,11</t>
+          <t>4,06; 8,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,93</t>
+          <t>1,64; 5,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,7</t>
+          <t>4,47; 8,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,2</t>
+          <t>2,75; 5,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,63</t>
+          <t>4,67; 7,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,75</t>
+          <t>2,38; 4,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,28</t>
+          <t>4,3; 7,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,53</t>
+          <t>6,91; 13,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,82</t>
+          <t>12,84; 20,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,65</t>
+          <t>4,74; 10,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,21</t>
+          <t>4,8; 10,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,47</t>
+          <t>2,77; 7,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 15,74</t>
+          <t>8,92; 16,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,65</t>
+          <t>2,23; 6,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,36</t>
+          <t>5,53; 10,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,32</t>
+          <t>5,37; 9,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,7; 17,13</t>
+          <t>11,79; 17,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,54</t>
+          <t>4,07; 7,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,26</t>
+          <t>5,94; 9,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 14,76</t>
+          <t>8,34; 14,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,36</t>
+          <t>6,09; 12,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 13,91</t>
+          <t>7,47; 14,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,1</t>
+          <t>4,28; 12,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,42</t>
+          <t>3,46; 8,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,94</t>
+          <t>2,73; 7,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,73</t>
+          <t>6,43; 13,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,87</t>
+          <t>2,78; 8,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,05</t>
+          <t>6,53; 10,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,78</t>
+          <t>4,74; 8,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,5</t>
+          <t>7,68; 12,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,99</t>
+          <t>4,04; 8,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,09</t>
+          <t>6,18; 14,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,41</t>
+          <t>3,43; 9,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,39</t>
+          <t>2,6; 8,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,85</t>
+          <t>1,76; 7,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,29</t>
+          <t>3,23; 10,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 13,93</t>
+          <t>5,56; 13,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,16</t>
+          <t>0,51; 5,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 11,2</t>
+          <t>5,34; 10,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,38</t>
+          <t>5,49; 10,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,42</t>
+          <t>2,03; 5,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,9</t>
+          <t>0,86; 3,51</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,94</t>
+          <t>4,46; 10,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,64</t>
+          <t>7,74; 15,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,59</t>
+          <t>7,06; 14,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,94; 13,43</t>
+          <t>7,13; 13,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,21</t>
+          <t>4,88; 11,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,03</t>
+          <t>8,86; 17,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 17,67</t>
+          <t>9,1; 17,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 13,66</t>
+          <t>8,29; 13,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,24</t>
+          <t>5,41; 9,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,8</t>
+          <t>9,14; 15,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,44; 15,29</t>
+          <t>9,67; 15,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,34</t>
+          <t>8,09; 12,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,95</t>
+          <t>5,26; 9,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,49</t>
+          <t>7,8; 12,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,87</t>
+          <t>2,64; 5,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,54</t>
+          <t>5,79; 10,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,31</t>
+          <t>2,43; 5,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,85</t>
+          <t>6,6; 10,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,87</t>
+          <t>2,63; 5,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,66</t>
+          <t>6,04; 9,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,03</t>
+          <t>4,25; 6,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,85; 10,9</t>
+          <t>7,83; 10,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,2</t>
+          <t>3,05; 5,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,1</t>
+          <t>6,33; 9,39</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,5</t>
+          <t>4,82; 8,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,7</t>
+          <t>2,02; 4,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,19</t>
+          <t>3,11; 6,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,44</t>
+          <t>2,41; 5,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,99</t>
+          <t>4,48; 7,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,68</t>
+          <t>2,01; 4,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,65</t>
+          <t>2,18; 4,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,5</t>
+          <t>2,94; 5,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,72</t>
+          <t>5,19; 7,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,34</t>
+          <t>2,33; 4,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,93</t>
+          <t>2,95; 4,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,41</t>
+          <t>3,04; 4,97</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,4</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,35</t>
+          <t>7,41; 9,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,73</t>
+          <t>5,05; 6,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,84</t>
+          <t>5,39; 7,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,05</t>
+          <t>4,49; 6,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,28</t>
+          <t>6,34; 8,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,2</t>
+          <t>4,67; 6,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,61</t>
+          <t>5,56; 6,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,01</t>
+          <t>5,66; 6,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,47</t>
+          <t>7,15; 8,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,2</t>
+          <t>5,1; 6,21</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,47</t>
+          <t>5,71; 6,88</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12122; 28520</t>
+          <t>11857; 28389</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26142; 49492</t>
+          <t>27145; 50399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12038; 30533</t>
+          <t>12676; 29300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18361; 44750</t>
+          <t>18227; 39122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8660; 24434</t>
+          <t>7820; 25260</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17545; 39323</t>
+          <t>18217; 39261</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21190; 45026</t>
+          <t>19446; 41026</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22542; 37127</t>
+          <t>23328; 38887</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23156; 46358</t>
+          <t>23788; 46749</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49116; 81308</t>
+          <t>50190; 82310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36488; 63547</t>
+          <t>37661; 65871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45387; 75641</t>
+          <t>46253; 72753</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11808; 30889</t>
+          <t>12528; 31484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22862; 45243</t>
+          <t>22943; 44323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11580; 30468</t>
+          <t>12196; 29519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14888; 38313</t>
+          <t>15180; 38879</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11224; 29572</t>
+          <t>11115; 28132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20951; 42477</t>
+          <t>21267; 43363</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9379; 25795</t>
+          <t>8589; 26494</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25273; 44809</t>
+          <t>24437; 44941</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26581; 51893</t>
+          <t>27450; 52704</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47157; 78566</t>
+          <t>48085; 78547</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25137; 48707</t>
+          <t>24370; 48284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44744; 75178</t>
+          <t>46281; 76230</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22272; 43138</t>
+          <t>22042; 44272</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40644; 67457</t>
+          <t>41617; 65758</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15445; 33915</t>
+          <t>15101; 32999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14693; 32277</t>
+          <t>15163; 31800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8656; 25058</t>
+          <t>9279; 25465</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29356; 53691</t>
+          <t>30421; 54931</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7589; 22368</t>
+          <t>7507; 22690</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19560; 36160</t>
+          <t>19698; 36626</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34569; 61004</t>
+          <t>35133; 63425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77816; 113934</t>
+          <t>78420; 115305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26021; 49355</t>
+          <t>26622; 49741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37916; 61616</t>
+          <t>39915; 61171</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29565; 52924</t>
+          <t>29910; 51586</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22684; 46231</t>
+          <t>22769; 46769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26204; 51463</t>
+          <t>27625; 53497</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12923; 37813</t>
+          <t>15958; 47152</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13088; 31288</t>
+          <t>12855; 30492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11062; 26997</t>
+          <t>10620; 28417</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25838; 49289</t>
+          <t>24908; 51857</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9790; 32658</t>
+          <t>11716; 34189</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48751; 80694</t>
+          <t>47683; 75904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37191; 66995</t>
+          <t>36177; 66696</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59318; 94683</t>
+          <t>58182; 93362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24992; 62967</t>
+          <t>32123; 68806</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11632; 30677</t>
+          <t>12571; 29208</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7341; 22134</t>
+          <t>7286; 21193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5497; 17722</t>
+          <t>5484; 17372</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3408; 14032</t>
+          <t>3629; 15017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7023; 21376</t>
+          <t>6716; 22358</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12070; 30591</t>
+          <t>12204; 29568</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1181; 11289</t>
+          <t>1123; 11473</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3262</t>
+          <t>0; 2897</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23100; 46036</t>
+          <t>21942; 44802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23340; 44868</t>
+          <t>23736; 45426</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8324; 23297</t>
+          <t>8737; 24231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3673; 15118</t>
+          <t>3715; 15210</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12092; 29633</t>
+          <t>12082; 29612</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20797; 42858</t>
+          <t>21218; 42909</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19277; 38380</t>
+          <t>18588; 38382</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18708; 36212</t>
+          <t>19314; 35250</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13388; 31190</t>
+          <t>13562; 32297</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24636; 47689</t>
+          <t>24801; 48406</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26536; 48258</t>
+          <t>24851; 48219</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20450; 35123</t>
+          <t>21857; 36111</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30478; 56211</t>
+          <t>29676; 54160</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51342; 82003</t>
+          <t>50631; 83151</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50619; 81994</t>
+          <t>51859; 81724</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43280; 64972</t>
+          <t>43246; 65184</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33839; 61208</t>
+          <t>32335; 60765</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51855; 82788</t>
+          <t>51676; 85276</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17414; 38555</t>
+          <t>17302; 37994</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30970; 59570</t>
+          <t>41689; 75307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15436; 33896</t>
+          <t>15506; 35278</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45585; 75268</t>
+          <t>45795; 75477</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17679; 40566</t>
+          <t>18197; 39570</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21447; 73560</t>
+          <t>46595; 73082</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54541; 88107</t>
+          <t>53279; 85764</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106490; 147921</t>
+          <t>106183; 147415</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39980; 70046</t>
+          <t>41099; 69685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56359; 119374</t>
+          <t>94384; 140038</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>54567</t>
+          <t>63385</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36311; 63259</t>
+          <t>35884; 62428</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15629; 36628</t>
+          <t>15707; 36055</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24536; 48204</t>
+          <t>24243; 48440</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10361; 41222</t>
+          <t>19238; 43749</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35674; 62623</t>
+          <t>35124; 62378</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17729; 38573</t>
+          <t>16579; 37600</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17717; 38422</t>
+          <t>18023; 38217</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>21205; 39507</t>
+          <t>24481; 46689</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>79669; 117879</t>
+          <t>79312; 118717</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37326; 69570</t>
+          <t>37416; 66697</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47180; 79161</t>
+          <t>47340; 77379</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32849; 72603</t>
+          <t>49499; 81045</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>212290; 275280</t>
+          <t>215378; 275818</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>255444; 320308</t>
+          <t>253974; 325624</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174325; 228532</t>
+          <t>171341; 229041</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153650; 236555</t>
+          <t>190405; 255818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>151993; 204526</t>
+          <t>151737; 203313</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>230061; 294681</t>
+          <t>225598; 290532</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>163810; 219660</t>
+          <t>165479; 222649</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>172841; 242043</t>
+          <t>207634; 261005</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>381713; 466311</t>
+          <t>376930; 462125</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>494687; 591726</t>
+          <t>499453; 596415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>355480; 430098</t>
+          <t>353845; 430711</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>352614; 461129</t>
+          <t>414681; 500325</t>
         </is>
       </c>
     </row>
